--- a/upload/ineficiencia-operacional.xlsx
+++ b/upload/ineficiencia-operacional.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="14">
   <si>
     <t>unidade</t>
   </si>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -614,21 +614,21 @@
         <v>3</v>
       </c>
       <c r="D16" s="3">
-        <v>1.2585999999999999</v>
+        <v>1.3657999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3">
-        <v>1.4035</v>
+        <v>1.7333000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -639,10 +639,10 @@
         <v>2025</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3">
-        <v>1.3419000000000001</v>
+        <v>1.4035</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -653,10 +653,10 @@
         <v>2025</v>
       </c>
       <c r="C19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3">
-        <v>1.5225</v>
+        <v>1.3419000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -667,10 +667,10 @@
         <v>2025</v>
       </c>
       <c r="C20" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3">
-        <v>1.3315999999999999</v>
+        <v>1.5225</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -681,10 +681,10 @@
         <v>2025</v>
       </c>
       <c r="C21" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="3">
-        <v>1.2706</v>
+        <v>1.3315999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -695,10 +695,10 @@
         <v>2025</v>
       </c>
       <c r="C22" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="3">
-        <v>1.4463999999999999</v>
+        <v>1.2706</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -709,10 +709,10 @@
         <v>2025</v>
       </c>
       <c r="C23" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" s="3">
-        <v>1.3363</v>
+        <v>1.4463999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -723,10 +723,10 @@
         <v>2025</v>
       </c>
       <c r="C24" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>1.2407999999999999</v>
+        <v>1.3363</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -737,10 +737,10 @@
         <v>2025</v>
       </c>
       <c r="C25" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="3">
-        <v>1.5421</v>
+        <v>1.2407999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -751,10 +751,10 @@
         <v>2025</v>
       </c>
       <c r="C26" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3">
-        <v>1.2774000000000001</v>
+        <v>1.5421</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -765,10 +765,10 @@
         <v>2025</v>
       </c>
       <c r="C27" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="3">
-        <v>1.3957999999999999</v>
+        <v>1.2774000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -779,10 +779,10 @@
         <v>2025</v>
       </c>
       <c r="C28" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" s="3">
-        <v>1.3585</v>
+        <v>1.3957999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -790,13 +790,13 @@
         <v>5</v>
       </c>
       <c r="B29" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D29" s="3">
-        <v>1.7447999999999997</v>
+        <v>1.3379000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -807,10 +807,10 @@
         <v>2026</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3">
-        <v>1.5481</v>
+        <v>1.7447999999999997</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -821,38 +821,38 @@
         <v>2026</v>
       </c>
       <c r="C31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="3">
-        <v>1.1846000000000001</v>
+        <v>1.5481</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" s="3">
-        <v>1.4442999999999999</v>
+        <v>1.4610999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" s="3">
-        <v>1.3426</v>
+        <v>1.1384000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -863,10 +863,10 @@
         <v>2025</v>
       </c>
       <c r="C34" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3">
-        <v>1.2255000000000003</v>
+        <v>1.4442999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -877,10 +877,10 @@
         <v>2025</v>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3">
-        <v>1.1579999999999999</v>
+        <v>1.3426</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -891,10 +891,10 @@
         <v>2025</v>
       </c>
       <c r="C36" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D36" s="3">
-        <v>1.1424000000000001</v>
+        <v>1.2255000000000003</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -905,10 +905,10 @@
         <v>2025</v>
       </c>
       <c r="C37" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>0.92569999999999997</v>
+        <v>1.1579999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -919,10 +919,10 @@
         <v>2025</v>
       </c>
       <c r="C38" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>1.2024999999999999</v>
+        <v>1.1424000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -933,10 +933,10 @@
         <v>2025</v>
       </c>
       <c r="C39" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D39" s="3">
-        <v>1.3017000000000001</v>
+        <v>0.92569999999999997</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -947,10 +947,10 @@
         <v>2025</v>
       </c>
       <c r="C40" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3">
-        <v>1.6136999999999999</v>
+        <v>1.2024999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -961,10 +961,10 @@
         <v>2025</v>
       </c>
       <c r="C41" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41" s="3">
-        <v>1.4704999999999999</v>
+        <v>1.3017000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -975,10 +975,10 @@
         <v>2025</v>
       </c>
       <c r="C42" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D42" s="3">
-        <v>1.3254999999999999</v>
+        <v>1.6136999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -989,10 +989,10 @@
         <v>2025</v>
       </c>
       <c r="C43" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D43" s="3">
-        <v>1.6149000000000002</v>
+        <v>1.4704999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1000,13 +1000,13 @@
         <v>6</v>
       </c>
       <c r="B44" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D44" s="3">
-        <v>1.5438000000000001</v>
+        <v>1.3254999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1014,13 +1014,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C45" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D45" s="3">
-        <v>1.5123</v>
+        <v>1.6181999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1031,52 +1031,52 @@
         <v>2026</v>
       </c>
       <c r="C46" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" s="3">
-        <v>0.87939999999999996</v>
+        <v>1.5438000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="3">
-        <v>1.5391999999999999</v>
+        <v>1.5123</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B48" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" s="3">
-        <v>1.7155</v>
+        <v>0.88049999999999995</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B49" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C49" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="3">
-        <v>1.5150999999999999</v>
+        <v>1.1097999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1087,10 +1087,10 @@
         <v>2025</v>
       </c>
       <c r="C50" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D50" s="3">
-        <v>1.4668000000000001</v>
+        <v>1.5391999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1101,10 +1101,10 @@
         <v>2025</v>
       </c>
       <c r="C51" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D51" s="3">
-        <v>1.3513999999999997</v>
+        <v>1.7155</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1115,10 +1115,10 @@
         <v>2025</v>
       </c>
       <c r="C52" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D52" s="3">
-        <v>1.4528000000000003</v>
+        <v>1.5150999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1129,10 +1129,10 @@
         <v>2025</v>
       </c>
       <c r="C53" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D53" s="3">
-        <v>1.4490000000000001</v>
+        <v>1.4668000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1143,10 +1143,10 @@
         <v>2025</v>
       </c>
       <c r="C54" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D54" s="3">
-        <v>1.4271</v>
+        <v>1.3537999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1157,10 +1157,10 @@
         <v>2025</v>
       </c>
       <c r="C55" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D55" s="3">
-        <v>1.4487000000000001</v>
+        <v>1.4476</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1171,10 +1171,10 @@
         <v>2025</v>
       </c>
       <c r="C56" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D56" s="3">
-        <v>1.4444999999999999</v>
+        <v>1.4489000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1185,10 +1185,10 @@
         <v>2025</v>
       </c>
       <c r="C57" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D57" s="3">
-        <v>1.5651999999999999</v>
+        <v>1.4271</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1199,10 +1199,10 @@
         <v>2025</v>
       </c>
       <c r="C58" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="3">
-        <v>1.4885999999999999</v>
+        <v>1.4487000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1210,13 +1210,13 @@
         <v>7</v>
       </c>
       <c r="B59" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D59" s="3">
-        <v>1.5723</v>
+        <v>1.4444999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1224,13 +1224,13 @@
         <v>7</v>
       </c>
       <c r="B60" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C60" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D60" s="3">
-        <v>1.633</v>
+        <v>1.5656000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1238,69 +1238,69 @@
         <v>7</v>
       </c>
       <c r="B61" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C61" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D61" s="3">
-        <v>2.3332999999999999</v>
+        <v>1.4887999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B62" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
       </c>
       <c r="D62" s="3">
-        <v>1.4294</v>
+        <v>1.5723</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B63" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C63" s="2">
         <v>2</v>
       </c>
       <c r="D63" s="3">
-        <v>1.4434</v>
+        <v>1.633</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B64" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C64" s="2">
         <v>3</v>
       </c>
       <c r="D64" s="3">
-        <v>1.6154999999999999</v>
+        <v>2.3243999999999998</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B65" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C65" s="2">
         <v>4</v>
       </c>
       <c r="D65" s="3">
-        <v>1.3332999999999999</v>
+        <v>1.6338999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1311,10 +1311,10 @@
         <v>2025</v>
       </c>
       <c r="C66" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D66" s="3">
-        <v>1.4978</v>
+        <v>1.4294</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1325,10 +1325,10 @@
         <v>2025</v>
       </c>
       <c r="C67" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D67" s="3">
-        <v>1.4668000000000001</v>
+        <v>1.4423999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1339,10 +1339,10 @@
         <v>2025</v>
       </c>
       <c r="C68" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3">
-        <v>1.5573999999999999</v>
+        <v>1.6154999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1353,10 +1353,10 @@
         <v>2025</v>
       </c>
       <c r="C69" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D69" s="3">
-        <v>1.5144</v>
+        <v>1.3332999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1367,10 +1367,10 @@
         <v>2025</v>
       </c>
       <c r="C70" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D70" s="3">
-        <v>1.7435</v>
+        <v>1.4978</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1381,10 +1381,10 @@
         <v>2025</v>
       </c>
       <c r="C71" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D71" s="3">
-        <v>1.4377</v>
+        <v>1.4668000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1395,10 +1395,10 @@
         <v>2025</v>
       </c>
       <c r="C72" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D72" s="3">
-        <v>1.4317</v>
+        <v>1.5573999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1409,10 +1409,10 @@
         <v>2025</v>
       </c>
       <c r="C73" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D73" s="3">
-        <v>1.6127999999999998</v>
+        <v>1.5137</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1420,13 +1420,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D74" s="3">
-        <v>1.7364999999999999</v>
+        <v>1.7431000000000001</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1434,13 +1434,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C75" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D75" s="3">
-        <v>1.6335</v>
+        <v>1.4377</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1448,83 +1448,83 @@
         <v>8</v>
       </c>
       <c r="B76" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C76" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D76" s="3">
-        <v>1.6364000000000001</v>
+        <v>1.4314</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B77" s="2">
         <v>2025</v>
       </c>
       <c r="C77" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D77" s="3">
-        <v>0</v>
+        <v>1.5329999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B78" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" s="3">
-        <v>0</v>
+        <v>1.7351000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B79" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" s="3">
-        <v>0</v>
+        <v>1.6309999999999998</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B80" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C80" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
-        <v>0</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B81" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C81" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>1.5582</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1535,7 +1535,7 @@
         <v>2025</v>
       </c>
       <c r="C82" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>2025</v>
       </c>
       <c r="C83" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>2025</v>
       </c>
       <c r="C84" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D84" s="3">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>2025</v>
       </c>
       <c r="C85" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D85" s="3">
         <v>0</v>
@@ -1591,7 +1591,7 @@
         <v>2025</v>
       </c>
       <c r="C86" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D86" s="3">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>2025</v>
       </c>
       <c r="C87" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D87" s="3">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>2025</v>
       </c>
       <c r="C88" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D88" s="3">
         <v>0</v>
@@ -1630,10 +1630,10 @@
         <v>9</v>
       </c>
       <c r="B89" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C89" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D89" s="3">
         <v>0</v>
@@ -1644,10 +1644,10 @@
         <v>9</v>
       </c>
       <c r="B90" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C90" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D90" s="3">
         <v>0</v>
@@ -1658,10 +1658,10 @@
         <v>9</v>
       </c>
       <c r="B91" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C91" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
@@ -1669,86 +1669,86 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B92" s="2">
         <v>2025</v>
       </c>
       <c r="C92" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D92" s="3">
-        <v>1.2245999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B93" s="2">
         <v>2025</v>
       </c>
       <c r="C93" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D93" s="3">
-        <v>1.0593999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B94" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C94" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D94" s="3">
-        <v>1.2124999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B95" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C95" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" s="3">
-        <v>0.998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B96" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C96" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D96" s="3">
-        <v>1.1479999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C97" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D97" s="3">
-        <v>1.1968000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1759,10 +1759,10 @@
         <v>2025</v>
       </c>
       <c r="C98" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D98" s="3">
-        <v>0.95820000000000016</v>
+        <v>1.2245999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1773,10 +1773,10 @@
         <v>2025</v>
       </c>
       <c r="C99" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D99" s="3">
-        <v>1.0831</v>
+        <v>1.0593999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1787,10 +1787,10 @@
         <v>2025</v>
       </c>
       <c r="C100" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D100" s="3">
-        <v>0.96030000000000004</v>
+        <v>1.2124999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1801,10 +1801,10 @@
         <v>2025</v>
       </c>
       <c r="C101" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D101" s="3">
-        <v>0.87670000000000003</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1815,10 +1815,10 @@
         <v>2025</v>
       </c>
       <c r="C102" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D102" s="3">
-        <v>0.84619999999999995</v>
+        <v>1.1479999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1829,10 +1829,10 @@
         <v>2025</v>
       </c>
       <c r="C103" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D103" s="3">
-        <v>0.90029999999999999</v>
+        <v>1.1968000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1840,13 +1840,13 @@
         <v>10</v>
       </c>
       <c r="B104" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D104" s="3">
-        <v>0.78700000000000003</v>
+        <v>0.95820000000000016</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1854,13 +1854,13 @@
         <v>10</v>
       </c>
       <c r="B105" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C105" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D105" s="3">
-        <v>0.69159999999999999</v>
+        <v>1.0831</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1868,111 +1868,111 @@
         <v>10</v>
       </c>
       <c r="B106" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C106" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D106" s="3">
-        <v>0.75509999999999999</v>
+        <v>0.96030000000000004</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B107" s="2">
         <v>2025</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D107" s="3">
-        <v>1.4968999999999999</v>
+        <v>0.87670000000000003</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
+        <v>10</v>
+      </c>
+      <c r="B108" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C108" s="2">
         <v>11</v>
       </c>
-      <c r="B108" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C108" s="2">
-        <v>2</v>
-      </c>
       <c r="D108" s="3">
-        <v>1.3492</v>
+        <v>0.84619999999999995</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B109" s="2">
         <v>2025</v>
       </c>
       <c r="C109" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D109" s="3">
-        <v>1.4683999999999999</v>
+        <v>0.90029999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B110" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C110" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D110" s="3">
-        <v>1.3237000000000001</v>
+        <v>0.78700000000000003</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B111" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C111" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D111" s="3">
-        <v>1.3811</v>
+        <v>0.69159999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B112" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C112" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D112" s="3">
-        <v>1.4875</v>
+        <v>0.75490000000000002</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B113" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C113" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D113" s="3">
-        <v>1.4806999999999999</v>
+        <v>0.79520000000000002</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1983,10 +1983,10 @@
         <v>2025</v>
       </c>
       <c r="C114" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D114" s="3">
-        <v>1.5384</v>
+        <v>1.4968999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1997,10 +1997,10 @@
         <v>2025</v>
       </c>
       <c r="C115" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D115" s="3">
-        <v>1.7829999999999999</v>
+        <v>1.3492</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2011,10 +2011,10 @@
         <v>2025</v>
       </c>
       <c r="C116" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D116" s="3">
-        <v>1.5165</v>
+        <v>1.4683999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2025,10 +2025,10 @@
         <v>2025</v>
       </c>
       <c r="C117" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D117" s="3">
-        <v>1.5310999999999999</v>
+        <v>1.3237000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2039,10 +2039,10 @@
         <v>2025</v>
       </c>
       <c r="C118" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D118" s="3">
-        <v>1.5356000000000001</v>
+        <v>1.3811</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2050,13 +2050,13 @@
         <v>11</v>
       </c>
       <c r="B119" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C119" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D119" s="3">
-        <v>1.7532000000000001</v>
+        <v>1.4875</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2064,13 +2064,13 @@
         <v>11</v>
       </c>
       <c r="B120" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C120" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D120" s="3">
-        <v>1.3285</v>
+        <v>1.4806999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2078,125 +2078,125 @@
         <v>11</v>
       </c>
       <c r="B121" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C121" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D121" s="3">
-        <v>1.5815999999999999</v>
+        <v>1.5384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B122" s="2">
         <v>2025</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D122" s="3">
-        <v>1.7951999999999999</v>
+        <v>1.7829999999999999</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B123" s="2">
         <v>2025</v>
       </c>
       <c r="C123" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D123" s="3">
-        <v>1.5901999999999998</v>
+        <v>1.5165</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B124" s="2">
         <v>2025</v>
       </c>
       <c r="C124" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D124" s="3">
-        <v>1.6193</v>
+        <v>1.5310999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C125" s="2">
         <v>12</v>
       </c>
-      <c r="B125" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C125" s="2">
-        <v>4</v>
-      </c>
       <c r="D125" s="3">
-        <v>1.7203999999999999</v>
+        <v>1.5356000000000001</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B126" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C126" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D126" s="3">
-        <v>1.5541</v>
+        <v>1.7532000000000001</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B127" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C127" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D127" s="3">
-        <v>1.5755999999999999</v>
+        <v>1.3285</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B128" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C128" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D128" s="3">
-        <v>1.5708</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B129" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C129" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D129" s="3">
-        <v>1.4536</v>
+        <v>1.6733</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2207,10 +2207,10 @@
         <v>2025</v>
       </c>
       <c r="C130" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D130" s="3">
-        <v>1.6705000000000001</v>
+        <v>1.7951999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2221,10 +2221,10 @@
         <v>2025</v>
       </c>
       <c r="C131" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D131" s="3">
-        <v>1.5023</v>
+        <v>1.5901999999999998</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2235,10 +2235,10 @@
         <v>2025</v>
       </c>
       <c r="C132" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D132" s="3">
-        <v>1.5672999999999999</v>
+        <v>1.6193</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2249,10 +2249,10 @@
         <v>2025</v>
       </c>
       <c r="C133" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D133" s="3">
-        <v>1.5276000000000001</v>
+        <v>1.7203999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2260,13 +2260,13 @@
         <v>12</v>
       </c>
       <c r="B134" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C134" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D134" s="3">
-        <v>1.6874</v>
+        <v>1.5541</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2274,13 +2274,13 @@
         <v>12</v>
       </c>
       <c r="B135" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C135" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D135" s="3">
-        <v>1.9696</v>
+        <v>1.5755999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2288,139 +2288,139 @@
         <v>12</v>
       </c>
       <c r="B136" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C136" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D136" s="3">
-        <v>1.2224999999999999</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B137" s="2">
         <v>2025</v>
       </c>
       <c r="C137" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D137" s="3">
-        <v>1.3052999999999999</v>
+        <v>1.4536</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B138" s="2">
         <v>2025</v>
       </c>
       <c r="C138" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D138" s="3">
-        <v>1.2967</v>
+        <v>1.6705000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B139" s="2">
         <v>2025</v>
       </c>
       <c r="C139" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D139" s="3">
-        <v>1.4623999999999997</v>
+        <v>1.5023</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B140" s="2">
         <v>2025</v>
       </c>
       <c r="C140" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D140" s="3">
-        <v>1.2698</v>
+        <v>1.5672999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B141" s="2">
         <v>2025</v>
       </c>
       <c r="C141" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D141" s="3">
-        <v>1.3299000000000001</v>
+        <v>1.5145999999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B142" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C142" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D142" s="3">
-        <v>1.4483999999999999</v>
+        <v>1.6167</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B143" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C143" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D143" s="3">
-        <v>1.4038999999999999</v>
+        <v>1.9274</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B144" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C144" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D144" s="3">
-        <v>1.3473999999999999</v>
+        <v>1.2435</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B145" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C145" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D145" s="3">
-        <v>1.2602</v>
+        <v>1.4792000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2431,10 +2431,10 @@
         <v>2025</v>
       </c>
       <c r="C146" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D146" s="3">
-        <v>1.3403</v>
+        <v>1.3052999999999999</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2445,10 +2445,10 @@
         <v>2025</v>
       </c>
       <c r="C147" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D147" s="3">
-        <v>1.1567000000000001</v>
+        <v>1.2967</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2459,10 +2459,10 @@
         <v>2025</v>
       </c>
       <c r="C148" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D148" s="3">
-        <v>1.2984</v>
+        <v>1.4623999999999997</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2470,13 +2470,13 @@
         <v>13</v>
       </c>
       <c r="B149" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C149" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D149" s="3">
-        <v>1.1263000000000001</v>
+        <v>1.2698</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2484,13 +2484,13 @@
         <v>13</v>
       </c>
       <c r="B150" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D150" s="3">
-        <v>1.2057</v>
+        <v>1.3299000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2498,13 +2498,153 @@
         <v>13</v>
       </c>
       <c r="B151" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C151" s="2">
+        <v>6</v>
+      </c>
+      <c r="D151" s="3">
+        <v>1.4483999999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>13</v>
+      </c>
+      <c r="B152" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C152" s="2">
+        <v>7</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1.4038999999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>13</v>
+      </c>
+      <c r="B153" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C153" s="2">
+        <v>8</v>
+      </c>
+      <c r="D153" s="3">
+        <v>1.3473999999999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>13</v>
+      </c>
+      <c r="B154" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C154" s="2">
+        <v>9</v>
+      </c>
+      <c r="D154" s="3">
+        <v>1.2602</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>13</v>
+      </c>
+      <c r="B155" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C155" s="2">
+        <v>10</v>
+      </c>
+      <c r="D155" s="3">
+        <v>1.3403</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>13</v>
+      </c>
+      <c r="B156" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C156" s="2">
+        <v>11</v>
+      </c>
+      <c r="D156" s="3">
+        <v>1.1567000000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>13</v>
+      </c>
+      <c r="B157" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C157" s="2">
+        <v>12</v>
+      </c>
+      <c r="D157" s="3">
+        <v>1.2902</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C158" s="2">
+        <v>1</v>
+      </c>
+      <c r="D158" s="3">
+        <v>1.1213</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>13</v>
+      </c>
+      <c r="B159" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C159" s="2">
+        <v>2</v>
+      </c>
+      <c r="D159" s="3">
+        <v>1.2089000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>13</v>
+      </c>
+      <c r="B160" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C160" s="2">
         <v>3</v>
       </c>
-      <c r="D151" s="3">
-        <v>1.0734999999999999</v>
+      <c r="D160" s="3">
+        <v>1.0811999999999999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>13</v>
+      </c>
+      <c r="B161" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C161" s="2">
+        <v>4</v>
+      </c>
+      <c r="D161" s="3">
+        <v>1.2435</v>
       </c>
     </row>
   </sheetData>

--- a/upload/ineficiencia-operacional.xlsx
+++ b/upload/ineficiencia-operacional.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="14">
   <si>
     <t>unidade</t>
   </si>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -614,7 +614,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="3">
-        <v>1.3931</v>
+        <v>1.4338</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -628,7 +628,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="3">
-        <v>1.6376000000000002</v>
+        <v>1.7055</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,16 +661,16 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" s="3">
-        <v>1.3980999999999999</v>
+        <v>1.8340000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -681,10 +681,10 @@
         <v>2025</v>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3">
-        <v>1.3511</v>
+        <v>1.3980999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -695,10 +695,10 @@
         <v>2025</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3">
-        <v>1.5268999999999999</v>
+        <v>1.3511</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -709,10 +709,10 @@
         <v>2025</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="3">
-        <v>1.34</v>
+        <v>1.5268999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -723,10 +723,10 @@
         <v>2025</v>
       </c>
       <c r="C24" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3">
-        <v>1.2791999999999999</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -737,10 +737,10 @@
         <v>2025</v>
       </c>
       <c r="C25" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="3">
-        <v>1.4463999999999999</v>
+        <v>1.2791999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -751,10 +751,10 @@
         <v>2025</v>
       </c>
       <c r="C26" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="3">
-        <v>1.3363</v>
+        <v>1.4463999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -765,10 +765,10 @@
         <v>2025</v>
       </c>
       <c r="C27" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>1.2512000000000001</v>
+        <v>1.3363</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -779,10 +779,10 @@
         <v>2025</v>
       </c>
       <c r="C28" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="3">
-        <v>1.5436000000000001</v>
+        <v>1.2512000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -793,10 +793,10 @@
         <v>2025</v>
       </c>
       <c r="C29" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="3">
-        <v>1.2774000000000001</v>
+        <v>1.5436000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -807,10 +807,10 @@
         <v>2025</v>
       </c>
       <c r="C30" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" s="3">
-        <v>1.4027000000000001</v>
+        <v>1.2774000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -821,10 +821,10 @@
         <v>2025</v>
       </c>
       <c r="C31" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" s="3">
-        <v>1.3129</v>
+        <v>1.4027000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -832,13 +832,13 @@
         <v>5</v>
       </c>
       <c r="B32" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D32" s="3">
-        <v>1.6214</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -849,10 +849,10 @@
         <v>2026</v>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="3">
-        <v>1.5452999999999999</v>
+        <v>1.5370999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -863,10 +863,10 @@
         <v>2026</v>
       </c>
       <c r="C34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3">
-        <v>1.4255</v>
+        <v>1.5452999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -877,10 +877,10 @@
         <v>2026</v>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="3">
-        <v>1.2853000000000001</v>
+        <v>1.4255</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -891,10 +891,10 @@
         <v>2026</v>
       </c>
       <c r="C36" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>1.3609</v>
+        <v>1.2951999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -905,38 +905,38 @@
         <v>2026</v>
       </c>
       <c r="C37" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>1.5606</v>
+        <v>1.3609</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C38" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D38" s="3">
-        <v>1.4442999999999999</v>
+        <v>1.5606</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C39" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D39" s="3">
-        <v>1.3426</v>
+        <v>1.4198</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -947,10 +947,10 @@
         <v>2025</v>
       </c>
       <c r="C40" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" s="3">
-        <v>1.2255000000000003</v>
+        <v>1.4442999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -961,10 +961,10 @@
         <v>2025</v>
       </c>
       <c r="C41" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" s="3">
-        <v>1.1579999999999999</v>
+        <v>1.3426</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -975,10 +975,10 @@
         <v>2025</v>
       </c>
       <c r="C42" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" s="3">
-        <v>1.1424000000000001</v>
+        <v>1.2255000000000003</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -989,10 +989,10 @@
         <v>2025</v>
       </c>
       <c r="C43" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" s="3">
-        <v>0.92569999999999997</v>
+        <v>1.1579999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1003,10 +1003,10 @@
         <v>2025</v>
       </c>
       <c r="C44" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D44" s="3">
-        <v>1.2024999999999999</v>
+        <v>1.1424000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1017,10 +1017,10 @@
         <v>2025</v>
       </c>
       <c r="C45" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D45" s="3">
-        <v>1.3017000000000001</v>
+        <v>0.92569999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1031,10 +1031,10 @@
         <v>2025</v>
       </c>
       <c r="C46" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D46" s="3">
-        <v>1.6227</v>
+        <v>1.2024999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1045,10 +1045,10 @@
         <v>2025</v>
       </c>
       <c r="C47" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D47" s="3">
-        <v>1.4704999999999999</v>
+        <v>1.3017000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1059,10 +1059,10 @@
         <v>2025</v>
       </c>
       <c r="C48" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D48" s="3">
-        <v>1.3305</v>
+        <v>1.6227</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1073,10 +1073,10 @@
         <v>2025</v>
       </c>
       <c r="C49" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D49" s="3">
-        <v>1.6092000000000002</v>
+        <v>1.4704999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1084,13 +1084,13 @@
         <v>6</v>
       </c>
       <c r="B50" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D50" s="3">
-        <v>1.532</v>
+        <v>1.3305</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1098,13 +1098,13 @@
         <v>6</v>
       </c>
       <c r="B51" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D51" s="3">
-        <v>1.5250999999999999</v>
+        <v>1.6092000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1115,10 +1115,10 @@
         <v>2026</v>
       </c>
       <c r="C52" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" s="3">
-        <v>0.871</v>
+        <v>1.532</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1129,10 +1129,10 @@
         <v>2026</v>
       </c>
       <c r="C53" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" s="3">
-        <v>1.1222000000000001</v>
+        <v>1.5250999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1143,10 +1143,10 @@
         <v>2026</v>
       </c>
       <c r="C54" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" s="3">
-        <v>1.0603</v>
+        <v>0.70679999999999998</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1157,52 +1157,52 @@
         <v>2026</v>
       </c>
       <c r="C55" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D55" s="3">
-        <v>1.0105</v>
+        <v>1.1068</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D56" s="3">
-        <v>1.5271999999999999</v>
+        <v>1.069</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C57" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D57" s="3">
-        <v>1.7208000000000001</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B58" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C58" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D58" s="3">
-        <v>1.5133000000000001</v>
+        <v>1.0918000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1213,10 +1213,10 @@
         <v>2025</v>
       </c>
       <c r="C59" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D59" s="3">
-        <v>1.4644999999999999</v>
+        <v>1.5271999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1227,10 +1227,10 @@
         <v>2025</v>
       </c>
       <c r="C60" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D60" s="3">
-        <v>1.3581000000000001</v>
+        <v>1.7208000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1241,10 +1241,10 @@
         <v>2025</v>
       </c>
       <c r="C61" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D61" s="3">
-        <v>1.4480999999999999</v>
+        <v>1.5133000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1255,10 +1255,10 @@
         <v>2025</v>
       </c>
       <c r="C62" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D62" s="3">
-        <v>1.4397</v>
+        <v>1.4644999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1269,10 +1269,10 @@
         <v>2025</v>
       </c>
       <c r="C63" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D63" s="3">
-        <v>1.4195</v>
+        <v>1.3581000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1283,10 +1283,10 @@
         <v>2025</v>
       </c>
       <c r="C64" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D64" s="3">
-        <v>1.4513</v>
+        <v>1.4468000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1297,10 +1297,10 @@
         <v>2025</v>
       </c>
       <c r="C65" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D65" s="3">
-        <v>1.4449000000000001</v>
+        <v>1.4397</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1311,10 +1311,10 @@
         <v>2025</v>
       </c>
       <c r="C66" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D66" s="3">
-        <v>1.5649</v>
+        <v>1.4195</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1325,10 +1325,10 @@
         <v>2025</v>
       </c>
       <c r="C67" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D67" s="3">
-        <v>1.4790000000000001</v>
+        <v>1.4513</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1336,13 +1336,13 @@
         <v>7</v>
       </c>
       <c r="B68" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D68" s="3">
-        <v>1.5723</v>
+        <v>1.4449000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1350,13 +1350,13 @@
         <v>7</v>
       </c>
       <c r="B69" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C69" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D69" s="3">
-        <v>1.6227</v>
+        <v>1.5649</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1364,13 +1364,13 @@
         <v>7</v>
       </c>
       <c r="B70" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C70" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D70" s="3">
-        <v>1.7870000000000001</v>
+        <v>1.4753000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1381,10 +1381,10 @@
         <v>2026</v>
       </c>
       <c r="C71" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D71" s="3">
-        <v>1.7090000000000001</v>
+        <v>1.5676000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1395,10 +1395,10 @@
         <v>2026</v>
       </c>
       <c r="C72" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D72" s="3">
-        <v>1.7082999999999999</v>
+        <v>1.6223000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1409,66 +1409,66 @@
         <v>2026</v>
       </c>
       <c r="C73" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D73" s="3">
-        <v>1.6886000000000001</v>
+        <v>1.7168000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B74" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74" s="3">
-        <v>1.4295</v>
+        <v>1.7059</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C75" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75" s="3">
-        <v>1.4435</v>
+        <v>1.7119999999999997</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B76" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C76" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D76" s="3">
-        <v>1.6137999999999999</v>
+        <v>1.6882999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B77" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C77" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D77" s="3">
-        <v>1.3332999999999999</v>
+        <v>1.7226999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1479,10 +1479,10 @@
         <v>2025</v>
       </c>
       <c r="C78" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78" s="3">
-        <v>1.4987999999999999</v>
+        <v>1.4295</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1493,10 +1493,10 @@
         <v>2025</v>
       </c>
       <c r="C79" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D79" s="3">
-        <v>1.4646999999999999</v>
+        <v>1.4435</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1507,10 +1507,10 @@
         <v>2025</v>
       </c>
       <c r="C80" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
-        <v>1.5511999999999999</v>
+        <v>1.6137999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1521,10 +1521,10 @@
         <v>2025</v>
       </c>
       <c r="C81" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D81" s="3">
-        <v>1.5134000000000001</v>
+        <v>1.3332999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1535,10 +1535,10 @@
         <v>2025</v>
       </c>
       <c r="C82" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D82" s="3">
-        <v>1.7444999999999999</v>
+        <v>1.4987999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1549,10 +1549,10 @@
         <v>2025</v>
       </c>
       <c r="C83" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D83" s="3">
-        <v>1.4382999999999999</v>
+        <v>1.4648000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1563,10 +1563,10 @@
         <v>2025</v>
       </c>
       <c r="C84" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D84" s="3">
-        <v>1.4335</v>
+        <v>1.5511999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1577,10 +1577,10 @@
         <v>2025</v>
       </c>
       <c r="C85" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D85" s="3">
-        <v>1.5206999999999999</v>
+        <v>1.5134000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1588,13 +1588,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D86" s="3">
-        <v>1.728</v>
+        <v>1.7444999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1602,13 +1602,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C87" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D87" s="3">
-        <v>1.6240000000000001</v>
+        <v>1.4382999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1616,13 +1616,13 @@
         <v>8</v>
       </c>
       <c r="B88" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C88" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D88" s="3">
-        <v>1.6351</v>
+        <v>1.4335</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1630,13 +1630,13 @@
         <v>8</v>
       </c>
       <c r="B89" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C89" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D89" s="3">
-        <v>1.5614999999999999</v>
+        <v>1.5210999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1647,10 +1647,10 @@
         <v>2026</v>
       </c>
       <c r="C90" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" s="3">
-        <v>1.3998999999999999</v>
+        <v>1.6919999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1661,80 +1661,80 @@
         <v>2026</v>
       </c>
       <c r="C91" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D91" s="3">
-        <v>1.2941</v>
+        <v>1.6240000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B92" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C92" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" s="3">
-        <v>0</v>
+        <v>1.5047999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B93" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C93" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93" s="3">
-        <v>0</v>
+        <v>1.5091000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B94" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C94" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B95" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C95" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D95" s="3">
-        <v>0</v>
+        <v>1.2950999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B96" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C96" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1.3738999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1745,7 +1745,7 @@
         <v>2025</v>
       </c>
       <c r="C97" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D97" s="3">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>2025</v>
       </c>
       <c r="C98" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D98" s="3">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>2025</v>
       </c>
       <c r="C99" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D99" s="3">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>2025</v>
       </c>
       <c r="C100" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D100" s="3">
         <v>0</v>
@@ -1801,7 +1801,7 @@
         <v>2025</v>
       </c>
       <c r="C101" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>2025</v>
       </c>
       <c r="C102" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D102" s="3">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>2025</v>
       </c>
       <c r="C103" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D103" s="3">
         <v>0</v>
@@ -1840,10 +1840,10 @@
         <v>9</v>
       </c>
       <c r="B104" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D104" s="3">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>9</v>
       </c>
       <c r="B105" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C105" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D105" s="3">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>9</v>
       </c>
       <c r="B106" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C106" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D106" s="3">
         <v>0</v>
@@ -1882,10 +1882,10 @@
         <v>9</v>
       </c>
       <c r="B107" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C107" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D107" s="3">
         <v>0</v>
@@ -1896,10 +1896,10 @@
         <v>9</v>
       </c>
       <c r="B108" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C108" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D108" s="3">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>2026</v>
       </c>
       <c r="C109" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D109" s="3">
         <v>0</v>
@@ -1921,86 +1921,86 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B110" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="3">
-        <v>1.2245999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B111" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C111" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" s="3">
-        <v>1.0593999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C112" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112" s="3">
-        <v>1.2126999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C113" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113" s="3">
-        <v>0.998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C114" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D114" s="3">
-        <v>1.1479999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B115" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C115" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D115" s="3">
-        <v>1.1968000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2011,10 +2011,10 @@
         <v>2025</v>
       </c>
       <c r="C116" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D116" s="3">
-        <v>0.95820000000000016</v>
+        <v>1.2245999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2025,10 +2025,10 @@
         <v>2025</v>
       </c>
       <c r="C117" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D117" s="3">
-        <v>1.0831</v>
+        <v>1.0593999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2039,10 +2039,10 @@
         <v>2025</v>
       </c>
       <c r="C118" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D118" s="3">
-        <v>0.96030000000000004</v>
+        <v>1.2126999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2053,10 +2053,10 @@
         <v>2025</v>
       </c>
       <c r="C119" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D119" s="3">
-        <v>0.87670000000000003</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2067,10 +2067,10 @@
         <v>2025</v>
       </c>
       <c r="C120" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D120" s="3">
-        <v>0.84619999999999995</v>
+        <v>1.1479999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2081,10 +2081,10 @@
         <v>2025</v>
       </c>
       <c r="C121" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D121" s="3">
-        <v>0.90029999999999999</v>
+        <v>1.1968000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2092,13 +2092,13 @@
         <v>10</v>
       </c>
       <c r="B122" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D122" s="3">
-        <v>0.78800000000000003</v>
+        <v>0.95820000000000016</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2106,13 +2106,13 @@
         <v>10</v>
       </c>
       <c r="B123" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C123" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D123" s="3">
-        <v>0.69159999999999999</v>
+        <v>1.0831</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2120,13 +2120,13 @@
         <v>10</v>
       </c>
       <c r="B124" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C124" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D124" s="3">
-        <v>0.76969999999999994</v>
+        <v>0.96030000000000004</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2134,13 +2134,13 @@
         <v>10</v>
       </c>
       <c r="B125" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C125" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D125" s="3">
-        <v>0.79810000000000003</v>
+        <v>0.87670000000000003</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2148,13 +2148,13 @@
         <v>10</v>
       </c>
       <c r="B126" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C126" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D126" s="3">
-        <v>0.76470000000000005</v>
+        <v>0.84619999999999995</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2162,111 +2162,111 @@
         <v>10</v>
       </c>
       <c r="B127" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C127" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D127" s="3">
-        <v>0.85389999999999999</v>
+        <v>0.90029999999999999</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B128" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
       </c>
       <c r="D128" s="3">
-        <v>1.4968999999999999</v>
+        <v>0.78800000000000003</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B129" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C129" s="2">
         <v>2</v>
       </c>
       <c r="D129" s="3">
-        <v>1.3492</v>
+        <v>0.69159999999999999</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B130" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C130" s="2">
         <v>3</v>
       </c>
       <c r="D130" s="3">
-        <v>1.4683999999999999</v>
+        <v>0.76969999999999994</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B131" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C131" s="2">
         <v>4</v>
       </c>
       <c r="D131" s="3">
-        <v>1.3237000000000001</v>
+        <v>0.79810000000000003</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B132" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C132" s="2">
         <v>5</v>
       </c>
       <c r="D132" s="3">
-        <v>1.3811</v>
+        <v>0.75539999999999996</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B133" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C133" s="2">
         <v>6</v>
       </c>
       <c r="D133" s="3">
-        <v>1.4875</v>
+        <v>0.85389999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B134" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C134" s="2">
         <v>7</v>
       </c>
       <c r="D134" s="3">
-        <v>1.4754</v>
+        <v>0.90610000000000013</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2277,10 +2277,10 @@
         <v>2025</v>
       </c>
       <c r="C135" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D135" s="3">
-        <v>1.5384</v>
+        <v>1.4968999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2291,10 +2291,10 @@
         <v>2025</v>
       </c>
       <c r="C136" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D136" s="3">
-        <v>1.7829999999999999</v>
+        <v>1.3492</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2305,10 +2305,10 @@
         <v>2025</v>
       </c>
       <c r="C137" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D137" s="3">
-        <v>1.5165</v>
+        <v>1.4683999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2319,10 +2319,10 @@
         <v>2025</v>
       </c>
       <c r="C138" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D138" s="3">
-        <v>1.5310999999999999</v>
+        <v>1.3237000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2333,10 +2333,10 @@
         <v>2025</v>
       </c>
       <c r="C139" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D139" s="3">
-        <v>1.5356000000000001</v>
+        <v>1.3811</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2344,13 +2344,13 @@
         <v>11</v>
       </c>
       <c r="B140" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D140" s="3">
-        <v>1.7471000000000001</v>
+        <v>1.4875</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2358,13 +2358,13 @@
         <v>11</v>
       </c>
       <c r="B141" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C141" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D141" s="3">
-        <v>1.3285</v>
+        <v>1.4754</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2372,13 +2372,13 @@
         <v>11</v>
       </c>
       <c r="B142" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C142" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D142" s="3">
-        <v>1.5650999999999999</v>
+        <v>1.5384</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2386,13 +2386,13 @@
         <v>11</v>
       </c>
       <c r="B143" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C143" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D143" s="3">
-        <v>1.8157000000000001</v>
+        <v>1.7829999999999999</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2400,13 +2400,13 @@
         <v>11</v>
       </c>
       <c r="B144" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C144" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D144" s="3">
-        <v>1.5181</v>
+        <v>1.5165</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2414,125 +2414,125 @@
         <v>11</v>
       </c>
       <c r="B145" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C145" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D145" s="3">
-        <v>1.5687</v>
+        <v>1.5310999999999999</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C146" s="2">
         <v>12</v>
       </c>
-      <c r="B146" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
       <c r="D146" s="3">
-        <v>1.7951999999999999</v>
+        <v>1.5356000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B147" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" s="3">
-        <v>1.5901999999999998</v>
+        <v>1.7471000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C148" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" s="3">
-        <v>1.6193</v>
+        <v>1.3285</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B149" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C149" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D149" s="3">
-        <v>1.7203999999999999</v>
+        <v>1.5777000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B150" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C150" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D150" s="3">
-        <v>1.5541</v>
+        <v>1.7903</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C151" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D151" s="3">
-        <v>1.5755999999999999</v>
+        <v>1.5185999999999999</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C152" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D152" s="3">
-        <v>1.5708</v>
+        <v>2.1095000000000002</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B153" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C153" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D153" s="3">
-        <v>1.4536</v>
+        <v>1.6685000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2543,10 +2543,10 @@
         <v>2025</v>
       </c>
       <c r="C154" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D154" s="3">
-        <v>1.6705000000000001</v>
+        <v>1.7951999999999999</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2557,10 +2557,10 @@
         <v>2025</v>
       </c>
       <c r="C155" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D155" s="3">
-        <v>1.5023</v>
+        <v>1.5901999999999998</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2571,10 +2571,10 @@
         <v>2025</v>
       </c>
       <c r="C156" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D156" s="3">
-        <v>1.5672999999999999</v>
+        <v>1.6193</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2585,10 +2585,10 @@
         <v>2025</v>
       </c>
       <c r="C157" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D157" s="3">
-        <v>1.5145999999999999</v>
+        <v>1.7203999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2596,13 +2596,13 @@
         <v>12</v>
       </c>
       <c r="B158" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C158" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D158" s="3">
-        <v>1.6257999999999999</v>
+        <v>1.5541</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2610,13 +2610,13 @@
         <v>12</v>
       </c>
       <c r="B159" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C159" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D159" s="3">
-        <v>1.9353</v>
+        <v>1.5755999999999999</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2624,13 +2624,13 @@
         <v>12</v>
       </c>
       <c r="B160" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C160" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D160" s="3">
-        <v>1.2087000000000001</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2638,13 +2638,13 @@
         <v>12</v>
       </c>
       <c r="B161" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C161" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D161" s="3">
-        <v>1.3596999999999999</v>
+        <v>1.4536</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2652,13 +2652,13 @@
         <v>12</v>
       </c>
       <c r="B162" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C162" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D162" s="3">
-        <v>1.2851999999999999</v>
+        <v>1.6705000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2666,139 +2666,139 @@
         <v>12</v>
       </c>
       <c r="B163" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C163" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D163" s="3">
-        <v>1.1808000000000001</v>
+        <v>1.5023</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B164" s="2">
         <v>2025</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D164" s="3">
-        <v>1.3052999999999999</v>
+        <v>1.5672999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B165" s="2">
         <v>2025</v>
       </c>
       <c r="C165" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D165" s="3">
-        <v>1.2967</v>
+        <v>1.5145999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B166" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C166" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" s="3">
-        <v>1.4623999999999997</v>
+        <v>1.6257999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B167" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C167" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D167" s="3">
-        <v>1.2698</v>
+        <v>1.9353</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B168" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C168" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D168" s="3">
-        <v>1.3299000000000001</v>
+        <v>1.1356999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B169" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C169" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D169" s="3">
-        <v>1.4483999999999999</v>
+        <v>1.3746</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B170" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C170" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D170" s="3">
-        <v>1.4038999999999999</v>
+        <v>1.2854000000000001</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B171" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C171" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D171" s="3">
-        <v>1.3462000000000001</v>
+        <v>1.1797</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B172" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C172" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D172" s="3">
-        <v>1.2602</v>
+        <v>1.2838000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2809,10 +2809,10 @@
         <v>2025</v>
       </c>
       <c r="C173" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D173" s="3">
-        <v>1.3403</v>
+        <v>1.3052999999999999</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2823,10 +2823,10 @@
         <v>2025</v>
       </c>
       <c r="C174" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D174" s="3">
-        <v>1.1567000000000001</v>
+        <v>1.2967</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2837,10 +2837,10 @@
         <v>2025</v>
       </c>
       <c r="C175" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D175" s="3">
-        <v>1.2902</v>
+        <v>1.4623999999999997</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2848,13 +2848,13 @@
         <v>13</v>
       </c>
       <c r="B176" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D176" s="3">
-        <v>1.1025</v>
+        <v>1.2698</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2862,13 +2862,13 @@
         <v>13</v>
       </c>
       <c r="B177" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C177" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D177" s="3">
-        <v>1.1637999999999999</v>
+        <v>1.3299000000000001</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2876,13 +2876,13 @@
         <v>13</v>
       </c>
       <c r="B178" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C178" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D178" s="3">
-        <v>1.0443</v>
+        <v>1.4483999999999999</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2890,13 +2890,13 @@
         <v>13</v>
       </c>
       <c r="B179" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C179" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D179" s="3">
-        <v>1.2005999999999999</v>
+        <v>1.4038999999999999</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2904,13 +2904,13 @@
         <v>13</v>
       </c>
       <c r="B180" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C180" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D180" s="3">
-        <v>1.2355</v>
+        <v>1.3462000000000001</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2918,13 +2918,153 @@
         <v>13</v>
       </c>
       <c r="B181" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C181" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D181" s="3">
-        <v>1.3091999999999999</v>
+        <v>1.2602</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>13</v>
+      </c>
+      <c r="B182" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C182" s="2">
+        <v>10</v>
+      </c>
+      <c r="D182" s="3">
+        <v>1.3403</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>13</v>
+      </c>
+      <c r="B183" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C183" s="2">
+        <v>11</v>
+      </c>
+      <c r="D183" s="3">
+        <v>1.1567000000000001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>13</v>
+      </c>
+      <c r="B184" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C184" s="2">
+        <v>12</v>
+      </c>
+      <c r="D184" s="3">
+        <v>1.2902</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>13</v>
+      </c>
+      <c r="B185" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C185" s="2">
+        <v>1</v>
+      </c>
+      <c r="D185" s="3">
+        <v>1.1023000000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>13</v>
+      </c>
+      <c r="B186" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C186" s="2">
+        <v>2</v>
+      </c>
+      <c r="D186" s="3">
+        <v>1.1625000000000001</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>13</v>
+      </c>
+      <c r="B187" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C187" s="2">
+        <v>3</v>
+      </c>
+      <c r="D187" s="3">
+        <v>1.0559999999999998</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>13</v>
+      </c>
+      <c r="B188" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C188" s="2">
+        <v>4</v>
+      </c>
+      <c r="D188" s="3">
+        <v>1.1589</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>13</v>
+      </c>
+      <c r="B189" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C189" s="2">
+        <v>5</v>
+      </c>
+      <c r="D189" s="3">
+        <v>1.2359</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>13</v>
+      </c>
+      <c r="B190" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C190" s="2">
+        <v>6</v>
+      </c>
+      <c r="D190" s="3">
+        <v>1.3032999999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>13</v>
+      </c>
+      <c r="B191" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C191" s="2">
+        <v>7</v>
+      </c>
+      <c r="D191" s="3">
+        <v>1.2897000000000001</v>
       </c>
     </row>
   </sheetData>
